--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lrc13\Documents\auto-certificates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3813BFE8-080C-4087-8EA4-26E9E4E7AAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F66D17-D3BF-4E69-821F-587925C318A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{916FC30F-F715-459F-927B-736DA7FC9EAF}"/>
   </bookViews>
@@ -50,13 +50,13 @@
     <t>عزة أحمد الخروصي</t>
   </si>
   <si>
+    <t>سامية المقبالي</t>
+  </si>
+  <si>
+    <t>أميمة عمر العوفي</t>
+  </si>
+  <si>
     <t>أمل الهاشمي</t>
-  </si>
-  <si>
-    <t>سامية المقبالي</t>
-  </si>
-  <si>
-    <t>أميمة عمر العوفي</t>
   </si>
 </sst>
 </file>
@@ -469,7 +469,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>71170130</v>
@@ -477,7 +477,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>71170130</v>
@@ -485,7 +485,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>71170130</v>
